--- a/Topic Relevant Comments - Nigeria/Banky Wellington/Final Say Faith.xlsx
+++ b/Topic Relevant Comments - Nigeria/Banky Wellington/Final Say Faith.xlsx
@@ -58,9 +58,6 @@
     <t>God's love language is FAITH.</t>
   </si>
   <si>
-    <t>Faith, one of God's love languages... Eyyy</t>
-  </si>
-  <si>
     <t>This is so intriguing.... God will continue to bless your Union . It's good to always have faith in God and watch Him perform His wonders and miracles in our lives . I use this couple as a point of reference, God... grant all my heart desires too ijn♥️</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>I love your faith beautiful couple, may God also give me a blessing that will shut many mouth up Amen</t>
   </si>
   <si>
-    <t>Hi, love this couple &amp; their love. I respect ur spirit if worship to God. Faith truly pleases God.</t>
-  </si>
-  <si>
     <t>ABBA father bless me with faith full husband and who knows u lord amen</t>
   </si>
   <si>
@@ -151,21 +145,21 @@
     <t>I have watched this video over and over again. I will marry well and trust (have faith)in God completely</t>
   </si>
   <si>
+    <t>God may not bring a man with all the wisdom but the fundamental basis to nurture the right fruits, sometimes he might need to draw water threw you. I believe you can ask God for a divinely ordained partner and the grace to to nurture that union. If you remember, Banky was not always like this, he ushered in all this when he started being around Susu. Just trust God to know what's good and give you what's yours.</t>
+  </si>
+  <si>
     <t>That's the beginning of everything. Been married now with a baby boy. Faithful God!</t>
   </si>
   <si>
     <t>Now i'm more convinced about the scripture that says do not be unequally yoked with and unbeliever, marrying the right person and a person with a relationship with God is very important to fulfilling destiny. i'm blessed by this and may God continue to make you a blessing to our lives and this generation.</t>
   </si>
   <si>
+    <t>i stand in Faith with you and your Wife. Anthony Shephered in the name of Jesus, you shall be a joyous parents of children. I would love to hear your testimony once GOD manifests it in flesh because He Will do it.</t>
+  </si>
+  <si>
     <t>There's nothing more beautiful than a beautiful couple who love Jesus genuinely. May the Holy Spirit continue to uphold your faith &amp; your home until Jesus returns</t>
   </si>
   <si>
-    <t>God may not bring a man with all the wisdom but the fundamental basis to nurture the right fruits, sometimes he might need to draw water threw you. I believe you can ask God for a divinely ordained partner and the grace to to nurture that union. If you remember, Banky was not always like this, he ushered in all this when he started being around Susu. Just trust God to know what's good and give you what's yours.</t>
-  </si>
-  <si>
-    <t>i stand in Faith with you and your Wife. Anthony Shephered in the name of Jesus, you shall be a joyous parents of children. I would love to hear your testimony once GOD manifests it in flesh because He Will do it.</t>
-  </si>
-  <si>
     <t>They are so cute praying to find such a Christian partner when i marry</t>
   </si>
   <si>
@@ -211,24 +205,27 @@
     <t>I will marry a believer</t>
   </si>
   <si>
+    <t>Having a relationship with God, strengthens our faith.</t>
+  </si>
+  <si>
     <t>This is what we call ...'A marriage that honors God' God bless you both in Jesus Name</t>
   </si>
   <si>
-    <t>Having a relationship with God, strengthens our faith.</t>
-  </si>
-  <si>
-    <t>Ever Faithful God, Promise Keeper</t>
-  </si>
-  <si>
     <t>I am proud of how you two are rooted in Christ. My faith got rekindled. Banky and susu. You have drown so many people to God through your testimony. And how you explained the case of Mary and Martha . God bless your marriage</t>
   </si>
   <si>
     <t>This is a great testimony, ur faith has made u whole..May d lord visit all waiting xouples</t>
   </si>
   <si>
+    <t>Relationship, worship , word</t>
+  </si>
+  <si>
     <t>This couple is blessed. I am inspired Banky and Susu♥️ With no doubt I will continue to serve the lord and may I marry a man who puts God first.</t>
   </si>
   <si>
+    <t>Love this couple so banky cab talk like this hahahhaha. Wow its good to have a husband or wife that knows God</t>
+  </si>
+  <si>
     <t>What is GOD's love language? Faith. Awwww I am taking notes.</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>Faith is one of God's love language, this is deep.i learnt a whole lot from this.</t>
   </si>
   <si>
-    <t>Love this couple so banky cab talk like this hahahhaha. Wow its good to have a husband or wife that knows God</t>
-  </si>
-  <si>
     <t>"One of God's love languages is Faith." Wow! I never thought about love languages in relation to my relationship with God. Thank you Banky and Adesua for inspiring and teaching us with your testimony!</t>
   </si>
   <si>
@@ -253,15 +247,15 @@
     <t>Heavenly Father please I want to marry a man of faith, one who will hold my hand through the storm.</t>
   </si>
   <si>
+    <t>This is High level of faith exhibited here. You two are true Christians</t>
+  </si>
+  <si>
+    <t>Was really touched by your word U show me what faith can really do and how much is good to be in one mind set I pray God bless your marriage and keep you going U guys are blessed I was crying when watching this</t>
+  </si>
+  <si>
     <t>When a true story is been told with sincerity, it administers healings to those that have been in a similar situation for years and are still seeking, believing in God. Banky you have faced your giant and you have been given victory by God. God bless you, your wife, and your child.</t>
   </si>
   <si>
-    <t>Was really touched by your word U show me what faith can really do and how much is good to be in one mind set I pray God bless your marriage and keep you going U guys are blessed I was crying when watching this</t>
-  </si>
-  <si>
-    <t>This is High level of faith exhibited here. You two are true Christians</t>
-  </si>
-  <si>
     <t>Marriage is beautiful... Taking a cue from this blissful couple</t>
   </si>
   <si>
@@ -340,6 +334,9 @@
     <t>Wow....apart from having a close relationship with God Have a man/husband who burn for God like you do or even more</t>
   </si>
   <si>
+    <t>Keep believing him and he will surprise you soon. Have hormonal test and sperm analysis for hubby! Keep yourself on folate and prenatal and hubby on wellman conception for two months. Track your ovulation with clear blue if can afford and make sure you bed your fertility time. Download flo app to help you to track. Join prayer with hubby with faith he will show up for you bcos he never disappoints</t>
+  </si>
+  <si>
     <t>When you marry God's will for you, every journey of life, no matter how difficult, seems less burdensome. I love your love Banky W and Adesua a.k.a SUSU. God has not finished with you yet. This is just the beginning.</t>
   </si>
   <si>
@@ -349,9 +346,6 @@
     <t>My marriage is blessed. Whenever my husband is, God has impacted him with wisdom in all areas already, Amen</t>
   </si>
   <si>
-    <t>Keep believing him and he will surprise you soon. Have hormonal test and sperm analysis for hubby! Keep yourself on folate and prenatal and hubby on wellman conception for two months. Track your ovulation with clear blue if can afford and make sure you bed your fertility time. Download flo app to help you to track. Join prayer with hubby with faith he will show up for you bcos he never disappoints</t>
-  </si>
-  <si>
     <t>Relationship and understanding the language of whoever you are in relationship with.....God bless you both.</t>
   </si>
   <si>
@@ -361,61 +355,64 @@
     <t>God also has a love language.....faith.. This is deep. God bless you</t>
   </si>
   <si>
+    <t>Waawooo this is so encouraging , I was going through the same in 2019-2020. Young couples need to watch this . I wish all men would be their for their wives like u. But I pray about in my religion.</t>
+  </si>
+  <si>
     <t>GOD is real. Faith over fear, Oluwakorede you see that husband that you want GOD will do it</t>
   </si>
   <si>
-    <t>Waawooo this is so encouraging , I was going through the same in 2019-2020. Young couples need to watch this . I wish all men would be their for their wives like u. But I pray about in my religion.</t>
-  </si>
-  <si>
     <t>God help me to trust you. I don't know how to. I will share my own testimony.</t>
   </si>
   <si>
     <t>God's love language is Faith, that is it for me, thank you Banky and Adesuwa, God please I don't want to be using you as 911...</t>
   </si>
   <si>
+    <t>Your faith in God is strong and i admire it, you both are amazing and i rejoice with you ❤</t>
+  </si>
+  <si>
     <t>You just woke up the giant in me with your words of faith... I also got married in 2017 nd it feels like eternity with all the external and internal pressures but my faith is rekindled today... God bless you</t>
   </si>
   <si>
     <t>Is it me Banky is talking to about one of God's love language which is faith???</t>
   </si>
   <si>
-    <t>Your faith in God is strong and i admire it, you both are amazing and i rejoice with you ❤</t>
-  </si>
-  <si>
     <t>It is so amazing when you hear of celebrity couples who are so involved in the word and the knowledge of God This is the definition of God ordained spouse I pray that God will continue to bless your union and for all of us that are well overdue for marriage and are still waiting, God will use this testimony as a point of contact to give us our own God ordained spouses</t>
   </si>
   <si>
     <t>Marry someone that listen to God!!!! Can't stress it enough</t>
   </si>
   <si>
+    <t>This is my testimony...God is faithful and worthy of all praises.. lol lets do the tired one</t>
+  </si>
+  <si>
     <t>I love the fact that he fears God God richly bless your marriage and child</t>
   </si>
   <si>
-    <t>This is my testimony...God is faithful and worthy of all praises.. lol lets do the tired one</t>
-  </si>
-  <si>
     <t>When God is present in a relationship, it's from glory to glory. More good news, more good news. May God bless your home. Love you both</t>
   </si>
   <si>
     <t>Been married for 8 years and the past 2 years have been very shaky and I've fallen out of love with my husband. However this couple is bringing me hope - their love is so beautiful and I'm beginning to see my own flaws now ... after 4 children I'm beginning to question my own attitude towards my husband and my own contribution towards the fading flame between us - as I've even moved out of our matrimonial home...</t>
   </si>
   <si>
+    <t>My Faith is re-ignited. Thanks my celebrity couple. Seeing you guys ministering to the world is the most beautiful and sexy thing I've seen in the past days</t>
+  </si>
+  <si>
+    <t>Thank u for doing this;my spirit is been lifting and putting me back on track with GOD;2 points stands out for me;susu loves language is spending time;do u know that is also one of GOD'S loves language is spending time with HIM ;that is one of the way u can know HIM and come against sin;the word of GOD says we are the replicate of him;as HE is in heaven;so are we are on earth 1john 4vs 17. 2.always seek to knows GOD'S plan and pls wait.our good LORD will continue blessing ur marriage.we are praying and rooting for u.GOD will continue to show u guys HIS love and continue to strength u in things of the kingdom.GOD loves u guys never doubt it❤</t>
+  </si>
+  <si>
+    <t>I will marry well in Jesus' name. Their marriage inspires me</t>
+  </si>
+  <si>
     <t>God is faithful, truly Father you are faithful, I trust in you and I know you will perfect my testimony Father I believe every vision,dreams and prophecies you have shown me n told me concerning my conception, I know soon by your grace this year i and my husband shall testify, help my unbelief and fears,show me mercy,I rely on you,thank you Lord for Banky and Adeusa,we are grateful Lord</t>
   </si>
   <si>
-    <t>My Faith is re-ignited. Thanks my celebrity couple. Seeing you guys ministering to the world is the most beautiful and sexy thing I've seen in the past days</t>
-  </si>
-  <si>
-    <t>I will marry well in Jesus' name. Their marriage inspires me</t>
+    <t>I love you both may God continue to be the center of your marriage</t>
   </si>
   <si>
     <t>Listening to you and your wife talk it just strengthen my faith, and brought a rebirth of trusting God more again. Your wife is right women go through alot , but just little is spoken about it.....thank you both for blessing us with this</t>
   </si>
   <si>
-    <t>Thank u for doing this;my spirit is been lifting and putting me back on track with GOD;2 points stands out for me;susu loves language is spending time;do u know that is also one of GOD'S loves language is spending time with HIM ;that is one of the way u can know HIM and come against sin;the word of GOD says we are the replicate of him;as HE is in heaven;so are we are on earth 1john 4vs 17. 2.always seek to knows GOD'S plan and pls wait.our good LORD will continue blessing ur marriage.we are praying and rooting for u.GOD will continue to show u guys HIS love and continue to strength u in things of the kingdom.GOD loves u guys never doubt it❤</t>
-  </si>
-  <si>
-    <t>I love you both may God continue to be the center of your marriage</t>
+    <t>This is a powerful testimony.I pray that my marriage becomes a fragrance to all around me.</t>
   </si>
   <si>
     <t>Your testimony is very inspiring, am happy you guys shared.</t>
@@ -427,9 +424,6 @@
     <t>Women? Marry a man that loves God cos what??!! I remain your number 1 online Inlaw. I love how you both love God</t>
   </si>
   <si>
-    <t>This is a powerful testimony.I pray that my marriage becomes a fragrance to all around me.</t>
-  </si>
-  <si>
     <t>This is beautiful, I hope I can trust and have faith in God half as much as you do. God bless your family</t>
   </si>
   <si>
@@ -463,40 +457,43 @@
     <t>Wow, this testimony is indeed a faith booster. A Home having christ has its bed rock, already have half it's problem solved. The remaining half lies on ones ability to trust fully in christ and obey every of his instructions per time. God bless you Ade and Banky.</t>
   </si>
   <si>
+    <t>1. Relationship 2. Worship 3. Word! But the key is obedience! God bless you for sharing your life testimony</t>
+  </si>
+  <si>
+    <t>Wow! I was so moved by this video. This is a great message/testimony! I thank God for you both. God is indeed a faithful God. I pray for discernment to fully trust God and to hear and know his voice when he speaks. I pray God gifts me a purpose partner like you both are to each other. God is good! Peace in the storm is a great thing to experience. Continue basking in his goodness. AMEN</t>
+  </si>
+  <si>
+    <t>You can't die, greater is He that is in you than He that is in the world. But a wife will be brought safely through childbirth, if they both continue in faith, love, and holiness, together with self-control. 1 Timothy 2:15 CEB The most important thing is not to have unforgiveness in your heart and bitterness in your soul. God is with you always even to the ends of time. Amen!!!!!!!</t>
+  </si>
+  <si>
+    <t>It is well my sister,I have pcos too,I was married for 10years, 10 years of waiting ain't no joke ,marriage crumbled but I believe God is still God,there is nothing impossible with God,this couple inspires me,love language is very vital in a relationship, most couples don't even understand how a love language works.</t>
+  </si>
+  <si>
+    <t>God's Love Language is faith. Wow thank you for this insight Banky</t>
+  </si>
+  <si>
+    <t>Dear future husband come and let tap into this kind of relationship Blessings</t>
+  </si>
+  <si>
+    <t>Wait on God and let him lead you in choosing the right one or else it marriage can be painful. I pray you get what they have in Jesus name!</t>
+  </si>
+  <si>
     <t>Am sharing tears as am listing to this is very important to marry ur soul mate and a child of God</t>
   </si>
   <si>
-    <t>1. Relationship 2. Worship 3. Word! But the key is obedience! God bless you for sharing your life testimony</t>
-  </si>
-  <si>
-    <t>You can't die, greater is He that is in you than He that is in the world. But a wife will be brought safely through childbirth, if they both continue in faith, love, and holiness, together with self-control. 1 Timothy 2:15 CEB The most important thing is not to have unforgiveness in your heart and bitterness in your soul. God is with you always even to the ends of time. Amen!!!!!!!</t>
-  </si>
-  <si>
-    <t>Wow! I was so moved by this video. This is a great message/testimony! I thank God for you both. God is indeed a faithful God. I pray for discernment to fully trust God and to hear and know his voice when he speaks. I pray God gifts me a purpose partner like you both are to each other. God is good! Peace in the storm is a great thing to experience. Continue basking in his goodness. AMEN</t>
-  </si>
-  <si>
-    <t>It is well my sister,I have pcos too,I was married for 10years, 10 years of waiting ain't no joke ,marriage crumbled but I believe God is still God,there is nothing impossible with God,this couple inspires me,love language is very vital in a relationship, most couples don't even understand how a love language works.</t>
-  </si>
-  <si>
-    <t>God's Love Language is faith. Wow thank you for this insight Banky</t>
-  </si>
-  <si>
-    <t>Dear future husband come and let tap into this kind of relationship Blessings</t>
-  </si>
-  <si>
-    <t>Wait on God and let him lead you in choosing the right one or else it marriage can be painful. I pray you get what they have in Jesus name!</t>
-  </si>
-  <si>
     <t>This is a healing message for me and my husband to be. I believe God will open doors that no man will close. Lord for the relationship my hubby have with you please always remember him</t>
   </si>
   <si>
     <t>This lady is blessed to have a husband like this....and this man has a wise prayerful woman</t>
   </si>
   <si>
+    <t>Your faith in God will help you heal</t>
+  </si>
+  <si>
     <t>Relationship is everything</t>
   </si>
   <si>
-    <t>Your faith in God will help you heal</t>
+    <t>This is so faith lifting</t>
   </si>
   <si>
     <t>"Faith in God helps you heal"</t>
@@ -505,6 +502,9 @@
     <t>My brother in-law and his wife are the next in line for this type of testimony ♥️❤️</t>
   </si>
   <si>
+    <t>This is a powerful testimony and a key to faith in God. May the Lord bless your home</t>
+  </si>
+  <si>
     <t>Banky A man filled with the word and spirit of God. I'm so encouraged by this testimony. Thank you for sharing your testimony. A lot of things I learnt from this 1. Have a relationship with God and be filled with his spirit 2. Be obedient to God 3. Trust and believe in God 4. Be sensitive to the leading of the Holy Spirit 5. Be with a man that has an intimate and personal relationship with God. A man that's not religious but has a true relationship with God. A man that hears and obeys God God bless you both</t>
   </si>
   <si>
@@ -514,39 +514,33 @@
     <t>Marry a man and woman who knows God oh. E get why</t>
   </si>
   <si>
-    <t>This is so faith lifting</t>
-  </si>
-  <si>
     <t>What a word . Trust God with your journey Have faith in God Build a relationship with God Hear God for yourself</t>
   </si>
   <si>
     <t>God's love language is faith! Wow! This hit different with context.</t>
   </si>
   <si>
-    <t>This is a powerful testimony and a key to faith in God. May the Lord bless your home</t>
+    <t>God's love language is FAITH!!! I love this guys thank you for sharing with us, God has DONE IT and WILL DO IT for any of us waiting for miracles in our lives in Jesus name!!</t>
   </si>
   <si>
     <t>"In your most painful moment, God is right there with you. In the midst of the storm, you will have His peace, comfort and strength". Words on marble! A true testimony on all levels. People maybe know that celebrities have issues, but maybe do not know that they go through this level of trials as well. Thank you Banky and Susu for testifying. Sometimes, praise really is a sacrifice. You have renewed the faith of many and God is proud of you for sharing. I wish you both more testimonies in your marriage.</t>
   </si>
   <si>
-    <t>God's love language is FAITH!!! I love this guys thank you for sharing with us, God has DONE IT and WILL DO IT for any of us waiting for miracles in our lives in Jesus name!!</t>
-  </si>
-  <si>
     <t>May the Love of Keep burning in your marriage.God is truly real.You guys just the best</t>
   </si>
   <si>
+    <t>This testimony will definitely bring people to This great God. Thank you so much for sharing My faith can not remain the same . NO WAY!!!</t>
+  </si>
+  <si>
+    <t>Glory to God! I'm indeed so blessed and encouraged...a lifetime message. God bless and keep your marriage. My favorite couple ❤️❤️❤️❤️❤️❤️</t>
+  </si>
+  <si>
+    <t>Our God is always faithful!All we need is trust and hold on to His promises..Have a relationship with God,worship God no matter the situation and live in the word of God..Love God,Love people❤️ God is a waymaker, miracle worker,promise keeper,light in every darkness</t>
+  </si>
+  <si>
     <t>I tap from this testimony God is really faithful</t>
   </si>
   <si>
-    <t>Glory to God! I'm indeed so blessed and encouraged...a lifetime message. God bless and keep your marriage. My favorite couple ❤️❤️❤️❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>Our God is always faithful!All we need is trust and hold on to His promises..Have a relationship with God,worship God no matter the situation and live in the word of God..Love God,Love people❤️ God is a waymaker, miracle worker,promise keeper,light in every darkness</t>
-  </si>
-  <si>
-    <t>This testimony will definitely bring people to This great God. Thank you so much for sharing My faith can not remain the same . NO WAY!!!</t>
-  </si>
-  <si>
     <t>You just showed me how much a couple's unified faith in God can move mountains no matter how insurmountable. Thanks for sharing your testimony, you both are indeed witnesses for Christ....much love and appreciation.</t>
   </si>
   <si>
@@ -586,9 +580,6 @@
     <t>I have enjoyed watching an listening in. Thanks a lot &amp; God bless your marriage &amp; family. He's faithful</t>
   </si>
   <si>
-    <t>Faith in God, his word and the mystery of heartfelt Praise will make happen to you what you CANNOT make happen for yourself. Matt6:33, Jere32:17, Mark 11:23-25 Stay blessed BankyShuZa</t>
-  </si>
-  <si>
     <t>Wow!... So touched by this.. FAITH speaks..</t>
   </si>
   <si>
@@ -598,25 +589,34 @@
     <t>I enjoyed the sermon.. FINAL SAY FAITH.. Relationship Worship The Word... This TESTIMONY will indeed be a step for others to climb.. FAITH INDEED..</t>
   </si>
   <si>
+    <t>This testimony is very uplifting seriously watching this made me cry. Indeed God is too faithful to fail.</t>
+  </si>
+  <si>
+    <t>This is the message I needed to keep my faith up to the next level...Simply relatable...May God come through for me and many other women seeking for the fruit of the womb...When the going gets though, let's brace ourselves with this word and be in tune with the Holy Spirit...Thank God for supportive and spirit-filled husband's....God bless you Banky and Adesua for this message</t>
+  </si>
+  <si>
     <t>Okay...so after listening to you both I cried my eyes out and I say to myself this is what I and my husband have been going through for 3 years of marriage and I say to myself my testimony is here¡ my faith is so strong right now and your God will definitely do ours. JESUS DID IT this month so I'm coming back with my evidence</t>
   </si>
   <si>
-    <t>This testimony is very uplifting seriously watching this made me cry. Indeed God is too faithful to fail.</t>
-  </si>
-  <si>
-    <t>This is the message I needed to keep my faith up to the next level...Simply relatable...May God come through for me and many other women seeking for the fruit of the womb...When the going gets though, let's brace ourselves with this word and be in tune with the Holy Spirit...Thank God for supportive and spirit-filled husband's....God bless you Banky and Adesua for this message</t>
-  </si>
-  <si>
     <t>Having Faith does not stop the hard times but it is the faith that helps you heal and pick yourself up again...Banky and Adesua your testimony is in season...Just right on time. Thank you for sharing and thank God for making this possible.</t>
   </si>
   <si>
+    <t>Wow am inspired by this testimony , father lord I need a God-fearing husband like banky, and I pray that I will be a understanding wife and a lovely mother in Jesus name amen</t>
+  </si>
+  <si>
+    <t>God is faithful,I'm still trusting him for my miracle baby</t>
+  </si>
+  <si>
     <t>O MY GOD THIS YOU GUYS TESTIMONY HAS TO ME TO HIGHER WAY OF KNOWING GOD HAVING FAITH ON HIM GLORY BE TO GOD AMEN</t>
   </si>
   <si>
-    <t>God is faithful,I'm still trusting him for my miracle baby</t>
-  </si>
-  <si>
     <t>I'm so bless I got this video... Your testimony is mind blowing... Lord I have learnt to trust in u throughout my relationship life... I believe to Man it's not possible... But I believe no one can battle with u.... Lord please take my relationship to a point we can say we have finally overcome... I love this... But what I can say to anyone "Date a man that fears and love God"... Because God is love.. David fears and love God that's why he was tag " a man after God's heart"...</t>
+  </si>
+  <si>
+    <t>wow am blessed without measures, it good to marry a christian. God will continue to bless your home and more babies to come in Jesus name. Amen</t>
+  </si>
+  <si>
+    <t>Oh! This is so inspiring! It just stirred my Spirit so much, it really gives me the assurance that God is at work in my Life. I got married in 2018 and have been battling with pcos, I used to get worried most of the times with many monthly tears, but I keep getting the reassurance from Abba even in that place of hurt, He still reassures me and so much encouragement from my husband too, and I tell you, since I started trusting Him wholely, I've been more at peace. I know Jesus will do it! God bless your Family Banky and Susu, for having a personal walk with God, and giving light to so many through this word of knowledge. Keep living victoriously!!!</t>
   </si>
 </sst>
 </file>
